--- a/themes/deposit.xlsx
+++ b/themes/deposit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -570,36 +570,36 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Подробнее по [ссылке]({{$temp.actualAccountLink}})</t>
+          <t xml:space="preserve">         Также отправляю вам ссылки на документы с подробным описанием [тарифного плана]꞉ https://uralsib.ru/api/directory-engine/files/rates/nakopitelnye-scheta_010626_w7zahekv.pdf</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Подробнее по [ссылке]({{$temp.actualAccountLink}}).</t>
+          <t xml:space="preserve">         Также отправляю вам ссылки на документы с подробным описанием [тарифного плана]: https://uralsib.ru/api/directory-engine/files/rates/nakopitelnye-scheta_010626_w7zahekv.pdf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>нестандартный символ двоеточия (U+A789) заменён на обычное двоеточие</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Также отправляю вам ссылки на документы с подробным описанием [тарифного плана]꞉ https://uralsib.ru/api/directory-engine/files/rates/nakopitelnye-scheta_010626_w7zahekv.pdf</t>
+          <t xml:space="preserve">        - Номинальный счет доступен для открытия родителям, опекунам или попечителям для зачисления средств социального характера꞉</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Также отправляю вам ссылки на документы с подробным описанием [тарифного плана]: https://uralsib.ru/api/directory-engine/files/rates/nakopitelnye-scheta_010626_w7zahekv.pdf</t>
+          <t xml:space="preserve">        - Номинальный счет доступен для открытия родителям, опекунам или попечителям для зачисления средств социального характера:</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -610,36 +610,36 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Подробнее по [ссылке]({{$temp.savingsAccountLink}})</t>
+          <t xml:space="preserve">        Для открытия вклада꞉</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Подробнее по [ссылке]({{$temp.savingsAccountLink}}).</t>
+          <t xml:space="preserve">        Для открытия вклада:</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>нестандартный символ двоеточия (U+A789) заменён на обычное двоеточие</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">        - Номинальный счет доступен для открытия родителям, опекунам или попечителям для зачисления средств социального характера꞉</t>
+          <t xml:space="preserve">        Для открытия вклада꞉</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">        - Номинальный счет доступен для открытия родителям, опекунам или попечителям для зачисления средств социального характера:</t>
+          <t xml:space="preserve">        Для открытия вклада:</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -650,371 +650,111 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        - Также отправляю вам ссылку на документ с подробным описанием [тарифного плана](https://uralsib.ru/api/directory-engine/files/rates/nomins_rur_120126_vr5mrcqa.pdf)</t>
+          <t xml:space="preserve">      Срочный вклад закроется автоматически в дату окончания. После этого банк перечислит все деньги на счет погашения꞉ сумму вклада и начисленные проценты.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        - Также отправляю вам ссылку на документ с подробным описанием [тарифного плана](https://uralsib.ru/api/directory-engine/files/rates/nomins_rur_120126_vr5mrcqa.pdf).</t>
+          <t xml:space="preserve">      Срочный вклад закроется автоматически в дату окончания. После этого банк перечислит все деньги на счет погашения: сумму вклада и начисленные проценты.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>нестандартный символ двоеточия (U+A789) заменён на обычное двоеточие</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">        - Оформить номинальный счет вы можете в [офисе банка]({{$temp.links["officeLink"]}})</t>
+          <t xml:space="preserve">      Закрыть вклад можно꞉</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">        - Оформить номинальный счет вы можете в [офисе банка]({{$temp.links["officeLink"]}}).</t>
+          <t xml:space="preserve">      Закрыть вклад можно:</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>нестандартный символ двоеточия (U+A789) заменён на обычное двоеточие</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">           Подробнее по [ссылке]({{$temp.links["nominalAccountLink"]}})</t>
+          <t xml:space="preserve">      Для закрытия вклада꞉</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">           Подробнее по [ссылке]({{$temp.links["nominalAccountLink"]}}).</t>
+          <t xml:space="preserve">      Для закрытия вклада:</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>нестандартный символ двоеточия (U+A789) заменён на обычное двоеточие</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - Ознакомиться со всеми доступными вариантами счетов, узнать подробнее об условиях и способах их оформления вы можете по [ссылке]({{$temp.depositLink}})</t>
+          <t xml:space="preserve">       Также отправляю вам ссылку на документ с подробным описанием тарифного плана꞉ https://uralsib.ru/api/directory-engine/files/rates/komfort-plyus_010626_ea1xw9j6.pdf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - Ознакомиться со всеми доступными вариантами счетов, узнать подробнее об условиях и способах их оформления вы можете по [ссылке]({{$temp.depositLink}}).</t>
+          <t xml:space="preserve">       Также отправляю вам ссылку на документ с подробным описанием тарифного плана: https://uralsib.ru/api/directory-engine/files/rates/komfort-plyus_010626_ea1xw9j6.pdf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>нестандартный символ двоеточия заменён на обычное</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125</v>
+        <v>314</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Для открытия вклада꞉</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Для открытия вклада:</t>
+          <t xml:space="preserve">          tranition: "/Deposits/Deposit/Close"</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>нестандартный символ двоеточия (U+A789) заменён на обычное двоеточие</t>
+          <t>похоже на опечатку в коде (не в тексте): ключ «tranition» вместо «transition» (пропущена буква «s») — кнопка может не работать. Не исправлял сам, но решил отметить</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130</v>
+        <v>316</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Для открытия вклада꞉</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Для открытия вклада:</t>
+          <t xml:space="preserve">          tranition: "/SomethingElse"</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>нестандартный символ двоеточия (U+A789) заменён на обычное двоеточие</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>137</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Срочный вклад закроется автоматически в дату окончания. После этого банк перечислит все деньги на счет погашения꞉ сумму вклада и начисленные проценты.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Срочный вклад закроется автоматически в дату окончания. После этого банк перечислит все деньги на счет погашения: сумму вклада и начисленные проценты.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>нестандартный символ двоеточия (U+A789) заменён на обычное двоеточие</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>139</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Закрыть вклад можно꞉</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Закрыть вклад можно:</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>нестандартный символ двоеточия (U+A789) заменён на обычное двоеточие</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>146</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Для закрытия вклада꞉</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Для закрытия вклада:</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>нестандартный символ двоеточия (U+A789) заменён на обычное двоеточие</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>168</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Оформить вклад вы можете в офисе банка или в «Уралсиб Онлайн». Подробнее по [ссылке]({{$temp.comfortDepositLink}})</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Оформить вклад вы можете в офисе банка или в «Уралсиб Онлайн». Подробнее по [ссылке]({{$temp.comfortDepositLink}}).</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>169</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Также отправляю вам ссылку на документ с подробным описанием тарифного плана꞉ https://uralsib.ru/api/directory-engine/files/rates/komfort-plyus_010626_ea1xw9j6.pdf</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Также отправляю вам ссылку на документ с подробным описанием тарифного плана: https://uralsib.ru/api/directory-engine/files/rates/komfort-plyus_010626_ea1xw9j6.pdf.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>нестандартный символ двоеточия заменён на обычное; добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>177</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Подробнее по [ссылке]({{$temp.incomeDepositLink}})</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Подробнее по [ссылке]({{$temp.incomeDepositLink}}).</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>184</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Подробнее по [ссылке]({{$temp.incomeDepositLink}})</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Подробнее по [ссылке]({{$temp.incomeDepositLink}}).</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>190</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Подробнее по [ссылке]({{$temp.DinamichDepositLink}})</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Подробнее по [ссылке]({{$temp.DinamichDepositLink}}).</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>197</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  OperationsAnswer: "Получить выписку с историей операций по вашему счету можно по [ссылке]({{ $temp.DepositOperationsLink }})"</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  OperationsAnswer: "Получить выписку с историей операций по вашему счету можно по [ссылке]({{ $temp.DepositOperationsLink }})."</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>314</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          tranition: "/Deposits/Deposit/Close"</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>похоже на опечатку в коде (не в тексте): ключ «tranition» вместо «transition» (пропущена буква «s») — кнопка может не работать. Не исправлял сам, но решил отметить</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>316</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          tranition: "/SomethingElse"</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
           <t>та же опечатка в коде: «tranition» вместо «transition»</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>386</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FinalReply: Также вы можете получить информацию по вашему вкладу [тут]({{ $temp.DepositConditionsLink }})</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FinalReply: Также вы можете получить информацию по вашему вкладу [тут]({{ $temp.DepositConditionsLink }}).</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>387</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Savings: Посмотреть информацию по вкладу можно в разделе «Сбережения» -&gt; «Счёт» -&gt; «О счёте», также доступно по [ссылке]({{$temp.DepositOperationsLink}})</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Savings: Посмотреть информацию по вкладу можно в разделе «Сбережения» -&gt; «Счёт» -&gt; «О счёте», также доступно по [ссылке]({{$temp.DepositOperationsLink}}).</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
         </is>
       </c>
     </row>
